--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CF8996-2B14-4B69-AF8C-008435235955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CC104F-2474-4130-8828-212AE2B81894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -147,9 +147,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>UpdatedHours</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -1231,24 +1231,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1263,12 +1263,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1286,22 +1286,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1425,7 @@
         <v>30</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>31</v>
@@ -1442,88 +1442,88 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
       </c>
       <c r="N2" t="s">
         <v>2</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>41</v>
       </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD2" t="s">
         <v>46</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1543,24 +1543,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1584,54 +1584,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1651,104 +1651,104 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="D1" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>108</v>
-      </c>
       <c r="C6" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1772,10 +1772,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1783,80 +1783,80 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1864,10 +1864,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CC104F-2474-4130-8828-212AE2B81894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E01269-2774-46BE-8522-122035493316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7245" yWindow="765" windowWidth="21600" windowHeight="11235" tabRatio="763" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="112">
   <si>
     <t>Rate Sheet</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Hagen Machhold</t>
   </si>
 </sst>
 </file>
@@ -1863,11 +1866,14 @@
       <c r="A9" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>80</v>
+      <c r="B9" t="s">
+        <v>111</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E01269-2774-46BE-8522-122035493316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A90414-8EA0-4B33-B601-77AA9823C632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7245" yWindow="765" windowWidth="21600" windowHeight="11235" tabRatio="763" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -300,9 +300,6 @@
     <t>Amy Xia</t>
   </si>
   <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>Indrajeet Singh</t>
   </si>
   <si>
@@ -379,6 +376,9 @@
   </si>
   <si>
     <t>Hagen Machhold</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
   </si>
 </sst>
 </file>
@@ -1248,10 +1248,10 @@
         <v>84</v>
       </c>
       <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
-      </c>
-      <c r="C2" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1266,12 +1266,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1289,22 +1289,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>31</v>
@@ -1448,7 +1448,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -1481,13 +1481,13 @@
         <v>2</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R2" t="s">
         <v>40</v>
@@ -1496,7 +1496,7 @@
         <v>40</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -1517,13 +1517,13 @@
         <v>45</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AB2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC2" t="s">
         <v>99</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>100</v>
       </c>
       <c r="AD2" t="s">
         <v>46</v>
@@ -1546,13 +1546,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1560,10 +1560,10 @@
         <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1619,7 +1619,7 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
@@ -1657,13 +1657,13 @@
         <v>62</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="D1" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1671,32 +1671,32 @@
         <v>74</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1704,21 +1704,21 @@
         <v>74</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>107</v>
-      </c>
       <c r="C6" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1726,32 +1726,32 @@
         <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A90414-8EA0-4B33-B601-77AA9823C632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF87789D-8CAF-4E90-8B82-DB86BD1E6BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -385,7 +385,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,6 +518,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -883,7 +890,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -902,6 +909,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1225,14 +1235,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -1243,7 +1253,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1262,14 +1272,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E443B5-FDCB-415B-A368-C107B8174FC6}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -1282,27 +1292,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B131D4C-C4A1-4B4C-93CE-09F4B7EA1E88}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -1315,34 +1325,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351367AD-7436-4842-8EB6-D7DC6164D492}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1437,7 +1447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1537,14 +1547,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D371A950-9E3A-42F2-B5C0-C3EFBC8CA0D4}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -1555,7 +1565,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1574,18 +1584,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC35A3B-4335-42C3-9C2A-D9EE03E3456F}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -1611,7 +1621,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1645,14 +1655,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -1666,7 +1676,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>74</v>
       </c>
@@ -1677,7 +1687,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>104</v>
       </c>
@@ -1688,7 +1698,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>104</v>
       </c>
@@ -1699,7 +1709,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>74</v>
       </c>
@@ -1710,7 +1720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>105</v>
       </c>
@@ -1721,7 +1731,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>74</v>
       </c>
@@ -1732,7 +1742,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>103</v>
       </c>
@@ -1743,7 +1753,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>96</v>
       </c>
@@ -1763,17 +1773,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1784,11 +1794,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C2" t="s">
@@ -1796,7 +1806,7 @@
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1807,7 +1817,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1818,18 +1828,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -1840,18 +1850,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1862,7 +1872,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF87789D-8CAF-4E90-8B82-DB86BD1E6BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598F7273-B6E5-41A3-8E9F-93538EDFECEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
   <si>
     <t>Rate Sheet</t>
   </si>
@@ -379,6 +379,18 @@
   </si>
   <si>
     <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Brian Zimmerman</t>
+  </si>
+  <si>
+    <t>Michael Graham</t>
+  </si>
+  <si>
+    <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Need to add on TT Beta Grp </t>
   </si>
 </sst>
 </file>
@@ -1235,14 +1247,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -1253,7 +1265,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1272,14 +1284,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E443B5-FDCB-415B-A368-C107B8174FC6}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -1292,27 +1304,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B131D4C-C4A1-4B4C-93CE-09F4B7EA1E88}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -1325,34 +1337,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351367AD-7436-4842-8EB6-D7DC6164D492}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1447,7 +1459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1547,14 +1559,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D371A950-9E3A-42F2-B5C0-C3EFBC8CA0D4}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -1565,7 +1577,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1584,18 +1596,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC35A3B-4335-42C3-9C2A-D9EE03E3456F}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -1621,7 +1633,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1655,14 +1667,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -1676,7 +1688,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>74</v>
       </c>
@@ -1687,7 +1699,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>104</v>
       </c>
@@ -1698,7 +1710,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>104</v>
       </c>
@@ -1709,7 +1721,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>74</v>
       </c>
@@ -1720,7 +1732,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>105</v>
       </c>
@@ -1731,7 +1743,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>74</v>
       </c>
@@ -1742,7 +1754,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>103</v>
       </c>
@@ -1753,7 +1765,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>96</v>
       </c>
@@ -1773,17 +1785,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1794,19 +1806,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>81</v>
+      <c r="B2" t="s">
+        <v>114</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1817,7 +1834,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1828,18 +1845,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>72</v>
+      <c r="B5" t="s">
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E5" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -1850,18 +1870,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>76</v>
+      <c r="B7" t="s">
+        <v>113</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1872,7 +1895,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598F7273-B6E5-41A3-8E9F-93538EDFECEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719B9B85-C23C-41C0-ABF5-9294EB01876E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
   <si>
     <t>Rate Sheet</t>
   </si>
@@ -282,9 +282,6 @@
     <t>Roman Debald</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
     <t>Bryan Loh</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t>Liz Hedgcock</t>
   </si>
   <si>
-    <t>Brian Zimmerman</t>
-  </si>
-  <si>
     <t>Michael Graham</t>
   </si>
   <si>
@@ -391,6 +385,15 @@
   </si>
   <si>
     <t xml:space="preserve">Need to add on TT Beta Grp </t>
+  </si>
+  <si>
+    <t>Qi Chen</t>
+  </si>
+  <si>
+    <t>Garrett Riffe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayati Arvind </t>
   </si>
 </sst>
 </file>
@@ -1256,24 +1259,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
         <v>84</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1288,12 +1291,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1311,22 +1314,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1450,7 +1453,7 @@
         <v>30</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>31</v>
@@ -1470,7 +1473,7 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -1503,13 +1506,13 @@
         <v>2</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R2" t="s">
         <v>40</v>
@@ -1518,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -1539,13 +1542,13 @@
         <v>45</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC2" t="s">
         <v>98</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>99</v>
       </c>
       <c r="AD2" t="s">
         <v>46</v>
@@ -1568,13 +1571,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1582,10 +1585,10 @@
         <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1641,7 +1644,7 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
@@ -1679,13 +1682,13 @@
         <v>62</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="D1" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1693,32 +1696,32 @@
         <v>74</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1726,21 +1729,21 @@
         <v>74</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>106</v>
-      </c>
       <c r="C6" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1748,32 +1751,32 @@
         <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1811,16 +1814,16 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1850,7 +1853,7 @@
         <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -1875,7 +1878,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
@@ -1889,10 +1892,13 @@
         <v>71</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,13 +1906,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
+++ b/TestData/LV_TMTT0013748_VerifyNewTitleRateSheetAvailability_CalculatedAmountOnTimeRecordManagerAfterAddingRateSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ACB5CA-395E-4D0A-B822-FDFBC7323962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD74678-6E83-4448-8D25-24F976521A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="984" windowWidth="23256" windowHeight="12456" tabRatio="763" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -1250,14 +1250,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -1287,14 +1287,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E443B5-FDCB-415B-A368-C107B8174FC6}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -1307,27 +1307,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B131D4C-C4A1-4B4C-93CE-09F4B7EA1E88}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -1340,34 +1340,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351367AD-7436-4842-8EB6-D7DC6164D492}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1562,14 +1562,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D371A950-9E3A-42F2-B5C0-C3EFBC8CA0D4}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1599,18 +1599,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC35A3B-4335-42C3-9C2A-D9EE03E3456F}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1670,14 +1670,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25574261-C7E9-4831-90EC-39FB8AD56B12}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>62</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>74</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>103</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>103</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>74</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>104</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>74</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>102</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>95</v>
       </c>
@@ -1788,17 +1788,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
